--- a/data/trans_orig/AIRE_2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>12415</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7088</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8237</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>11030</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19985</t>
+          <t>20202</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22879</t>
+          <t>23250</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35517</t>
+          <t>35616</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36733</t>
+          <t>37155</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52208</t>
+          <t>52999</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>17626</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23382</t>
+          <t>23601</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9465</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>905</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14864</t>
+          <t>15029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>539</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8981</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11820</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12529</t>
+          <t>13229</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22229</t>
+          <t>22591</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11297</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21509</t>
+          <t>21938</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27563</t>
+          <t>27176</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41107</t>
+          <t>41226</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,14%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18418</t>
+          <t>17771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10756</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12764</t>
+          <t>12624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26290</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7454</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>13476</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>376</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9360</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15212</t>
+          <t>15528</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11993</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21256</t>
+          <t>21331</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17412</t>
+          <t>17183</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29670</t>
+          <t>29842</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,74%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>807</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6646</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>8275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12145</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>392</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9154</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11261</t>
+          <t>11812</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13343</t>
+          <t>14014</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>13033</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22989</t>
+          <t>22294</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21424</t>
+          <t>21280</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>74833</t>
+          <t>75417</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16954</t>
+          <t>17719</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>31517</t>
+          <t>31553</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>45499</t>
+          <t>45041</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>109912</t>
+          <t>110538</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,51%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13355</t>
+          <t>14426</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47347</t>
+          <t>47473</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20644</t>
+          <t>19792</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34728</t>
+          <t>34315</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36060</t>
+          <t>37008</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>75448</t>
+          <t>75803</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14817</t>
+          <t>14642</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16764</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27238</t>
+          <t>27122</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14524</t>
+          <t>13461</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20470</t>
+          <t>20441</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>762</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10198</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11367</t>
+          <t>11794</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23656</t>
+          <t>23720</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14596</t>
+          <t>14616</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28086</t>
+          <t>27612</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29611</t>
+          <t>29074</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>48826</t>
+          <t>47255</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>47,48%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18757</t>
+          <t>18719</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11626</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24289</t>
+          <t>23921</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>23834</t>
+          <t>23802</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>39136</t>
+          <t>39384</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,57%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>15633</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8350</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20906</t>
+          <t>19456</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9959</t>
+          <t>9190</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>13370</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>19303</t>
+          <t>19511</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>502</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>7130</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>932</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>10219</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>20196</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13535</t>
+          <t>14133</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>26929</t>
+          <t>27263</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,9%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12681</t>
+          <t>12265</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>11922</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>21308</t>
+          <t>21429</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>10863</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>12810</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>10217</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>905</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>8238</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>15862</t>
+          <t>15975</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>9402</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>24028</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11838</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>27138</t>
+          <t>26625</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>24646</t>
+          <t>24554</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>46414</t>
+          <t>45445</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>51213</t>
+          <t>50625</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>128317</t>
+          <t>134874</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>57702</t>
+          <t>58022</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>83768</t>
+          <t>83807</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>117713</t>
+          <t>120038</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>207623</t>
+          <t>226250</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>42,9%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>64462</t>
+          <t>61551</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>110934</t>
+          <t>111293</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>101002</t>
+          <t>100362</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>129664</t>
+          <t>129198</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>174762</t>
+          <t>170648</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>233300</t>
+          <t>231893</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>43,97%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>22748</t>
+          <t>21765</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>44638</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>35742</t>
+          <t>35249</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>57977</t>
+          <t>57758</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>64220</t>
+          <t>64706</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>96899</t>
+          <t>96927</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>19011</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>40208</t>
+          <t>40328</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>20875</t>
+          <t>20446</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>38729</t>
+          <t>38593</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>46088</t>
+          <t>43929</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>73076</t>
+          <t>70916</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2612</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6470</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3795</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1438</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8205</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,21%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4173</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1758</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8197</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>13,44%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>26,39%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2928</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6962</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>14,13%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>11</t>
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6723</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12415</t>
+          <t>11757</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>331</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>26676</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20252</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>32396</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>57,82%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>43,9%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>70,22%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15412</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11030</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>49,56%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>35,47%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>64,96%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29419</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23250</t>
+          <t>10820</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35616</t>
+          <t>19687</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>44831</t>
+          <t>41906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37155</t>
+          <t>34386</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52999</t>
+          <t>49836</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>64,56%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11769</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6750</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18133</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>25,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,63%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>39,3%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4828</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2215</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9189</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,55%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17626</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16286</t>
+          <t>16598</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10743</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23601</t>
+          <t>24074</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2835</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6714</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5382</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9427</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17,31%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>30,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15029</t>
+          <t>13720</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>46135</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>46135</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>46135</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>31097</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>31097</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>31097</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49285</t>
+          <t>31058</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49285</t>
+          <t>31058</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49285</t>
+          <t>31058</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>80382</t>
+          <t>77193</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>80382</t>
+          <t>77193</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>80382</t>
+          <t>77193</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,107 +1402,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3114</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7882</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3318</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1131</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9281</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,5%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>977</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4377</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1657</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8441</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13,07%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>25,2%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2131</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5289</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>14,7%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12346</t>
+          <t>11581</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16317</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11479</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21733</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>48,72%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>34,27%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>64,89%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>17608</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13229</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>22591</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>48,95%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>36,77%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>62,8%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11510</t>
+          <t>12384</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21938</t>
+          <t>22684</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,17 +1703,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>34399</t>
+          <t>33834</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27176</t>
+          <t>26300</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41226</t>
+          <t>40911</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,66%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5810</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2245</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10791</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>32,22%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12555</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8241</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17771</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>34,9%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>49,4%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>18285</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>18481</t>
+          <t>18529</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>12636</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>25650</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3873</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1362</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8208</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>11,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>24,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>3681</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1293</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7361</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20,46%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8779</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>7768</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>13394</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>33492</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>33492</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>33492</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>35975</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>35975</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>35975</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34933</t>
+          <t>36250</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34933</t>
+          <t>36250</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34933</t>
+          <t>36250</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>70908</t>
+          <t>69742</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>70908</t>
+          <t>69742</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>70908</t>
+          <t>69742</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2688</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,13%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2725</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3244</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>14,91%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3287</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>316</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2977</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1084</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>6384</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>12,33%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>26,43%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>5697</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2608</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>9805</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>31,17%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>14,27%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>53,65%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>8847</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15528</t>
+          <t>13165</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13962</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9801</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>17742</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>57,8%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>40,57%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>73,45%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>6938</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3739</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10439</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>37,96%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>20,46%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>57,12%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11277</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21331</t>
+          <t>10544</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>23555</t>
+          <t>20682</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17183</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29842</t>
+          <t>26646</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,42%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3385</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1270</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7801</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>14,02%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>32,3%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>3137</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>807</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6754</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>17,16%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>36,96%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3584</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>881</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11557</t>
+          <t>12307</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3054</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6195</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>12,64%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>25,64%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4975</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>10,9%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>27,22%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>322</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11812</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>24156</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>24156</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>24156</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>18276</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>18276</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>18276</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>17859</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>17859</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>17859</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>46817</t>
+          <t>42015</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46817</t>
+          <t>42015</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46817</t>
+          <t>42015</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14014</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13033</t>
+          <t>12088</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22294</t>
+          <t>20211</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>21522</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>15480</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>28573</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>31,51%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>22,66%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>41,83%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>44702</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>21280</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>75417</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>44,79%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>21,32%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>75,57%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>24199</t>
+          <t>18410</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17719</t>
+          <t>12539</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>31553</t>
+          <t>25960</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>68901</t>
+          <t>39932</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>45041</t>
+          <t>31017</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>110538</t>
+          <t>50971</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>36,75%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>25076</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>18708</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>32752</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>36,71%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>27,39%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>47,95%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>32204</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>14426</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>47473</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>32,27%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>14,46%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>47,57%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>27103</t>
+          <t>30094</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19792</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34315</t>
+          <t>37433</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>59307</t>
+          <t>55170</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>37008</t>
+          <t>44958</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>75803</t>
+          <t>64955</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>10183</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>5758</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>16095</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>14,91%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>8,43%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>8067</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>2475</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>14642</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>8,08%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>14,67%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>13696</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>18582</t>
+          <t>18368</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27122</t>
+          <t>26671</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>5245</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2541</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>11599</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>16,98%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>7587</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>2171</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>13461</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>12897</t>
+          <t>11919</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20441</t>
+          <t>18128</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>68303</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>68303</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>68303</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>99802</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>99802</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>99802</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>74234</t>
+          <t>70408</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>74234</t>
+          <t>70408</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>74234</t>
+          <t>70408</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>174036</t>
+          <t>138711</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>174036</t>
+          <t>138711</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>174036</t>
+          <t>138711</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2494</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>6648</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>12,06%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>1656</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5311</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5858</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>12,79%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2857</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>6926</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9282</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>18636</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>13186</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>25679</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>33,82%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>23,93%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>46,6%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>16969</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>11794</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>23720</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>40,87%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>28,41%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>57,13%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>20777</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14616</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27612</t>
+          <t>18916</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>37745</t>
+          <t>32385</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29074</t>
+          <t>25309</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>47255</t>
+          <t>41388</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>17015</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>11341</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>23012</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>30,88%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>20,58%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>41,76%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>13639</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>8522</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>18719</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>32,85%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>20,53%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>45,08%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>17571</t>
+          <t>13629</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11888</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23921</t>
+          <t>18632</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>31210</t>
+          <t>30644</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>23802</t>
+          <t>23408</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>39384</t>
+          <t>38208</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>9721</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>5351</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>15968</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>17,64%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>28,98%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>4009</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>1854</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>7557</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>9,65%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>18,2%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>13200</t>
+          <t>13464</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19456</t>
+          <t>20687</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>7238</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>3632</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>12533</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>13,14%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>22,74%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>5246</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>2302</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>9190</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13370</t>
+          <t>9720</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>12853</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>19511</t>
+          <t>19153</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>55104</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>55104</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>55104</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>41519</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>41519</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>41519</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>58004</t>
+          <t>38295</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>58004</t>
+          <t>38295</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>58004</t>
+          <t>38295</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>99522</t>
+          <t>93398</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>99522</t>
+          <t>93398</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>99522</t>
+          <t>93398</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>4142</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>14,06%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2576</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>7130</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>10,98%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>30,39%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>475</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>3589</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9535</t>
+          <t>9994</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>12343</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>7423</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>17338</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>41,9%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>25,2%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>58,86%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>4856</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>2319</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>8330</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>20,69%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>35,5%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20196</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>17386</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>14133</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27263</t>
+          <t>23430</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>43,61%</t>
         </is>
       </c>
     </row>
@@ -4356,72 +4356,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>6700</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>3208</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>11443</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>22,75%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>10,89%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>38,85%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>8269</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>4695</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>12265</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>35,24%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>20,01%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>52,27%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11922</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>15184</t>
+          <t>15030</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9968</t>
+          <t>9669</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>21429</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,58%</t>
         </is>
       </c>
     </row>
@@ -4469,72 +4469,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>5645</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2218</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>10673</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>19,16%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>7,53%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>36,23%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>1372</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>4405</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3742</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>5556</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>2489</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>10863</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>17,21%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>12810</t>
+          <t>12675</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -4582,72 +4582,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>3779</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>8447</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>12,83%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>28,68%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>6393</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>3244</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>10217</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>27,24%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>13,82%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>43,54%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>10695</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>15975</t>
+          <t>16725</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>29455</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>29455</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>29455</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>23466</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>23466</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>23466</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>55749</t>
+          <t>53728</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>55749</t>
+          <t>53728</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>55749</t>
+          <t>53728</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>16264</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>11056</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>24099</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>15781</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>9062</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>24028</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>18161</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>9959</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>26625</t>
+          <t>23876</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>33942</t>
+          <t>32525</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>24554</t>
+          <t>24040</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>45445</t>
+          <t>42966</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>62098</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>50591</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>74616</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>24,2%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>19,71%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>29,07%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>76036</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>50625</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>134874</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>30,4%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>20,24%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>53,92%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>70590</t>
+          <t>45971</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>58022</t>
+          <t>36598</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>83807</t>
+          <t>56833</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>146626</t>
+          <t>108069</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>120038</t>
+          <t>93409</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>226250</t>
+          <t>125446</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>105747</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>91012</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>119933</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>41,2%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>35,46%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>46,73%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>94070</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>61551</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>111293</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>37,61%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>24,61%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>44,49%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>114417</t>
+          <t>91518</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>100362</t>
+          <t>78765</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>129198</t>
+          <t>102524</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>208486</t>
+          <t>197265</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>170648</t>
+          <t>179349</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>231893</t>
+          <t>217283</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>45,76%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>46515</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>36665</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>59441</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>14,29%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>23,16%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>33967</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>21765</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>44101</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>17,63%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>46232</t>
+          <t>34134</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>35249</t>
+          <t>26500</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>57758</t>
+          <t>43620</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>80199</t>
+          <t>80649</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>64706</t>
+          <t>66375</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>96927</t>
+          <t>95551</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>26023</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>18797</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>35203</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>10,14%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>30281</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>19219</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>40328</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>12,11%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>27881</t>
+          <t>30258</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>20446</t>
+          <t>22776</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>38593</t>
+          <t>39977</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>58162</t>
+          <t>56280</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>43929</t>
+          <t>44676</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>70916</t>
+          <t>68442</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>256646</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>256646</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>256646</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>250134</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>250134</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>250134</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>277281</t>
+          <t>218142</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>277281</t>
+          <t>218142</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>277281</t>
+          <t>218142</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>527415</t>
+          <t>474788</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>527415</t>
+          <t>474788</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>527415</t>
+          <t>474788</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
